--- a/resources/templates/standard/L3100-02.xlsx
+++ b/resources/templates/standard/L3100-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>계 측 기   이 력 카 드</t>
   </si>
@@ -632,9 +635,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="40.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -668,14 +673,14 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4">
         <f>IF($I$2="","",VLOOKUP($I$2,#REF!,2,0))</f>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4">
@@ -687,14 +692,14 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4">
         <f>IF($I$2="","",VLOOKUP($I$2,#REF!,4,0))</f>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4">
@@ -706,14 +711,14 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4">
         <f>IF($I$2="","",VLOOKUP($I$2,#REF!,5,0))</f>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4">
@@ -725,14 +730,14 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
         <f>IF($I$2="","",VLOOKUP($I$2,#REF!,8,0))</f>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4">
@@ -744,7 +749,7 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -911,7 +916,7 @@
     </row>
     <row r="23" ht="22.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -924,19 +929,19 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -976,7 +981,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -989,26 +994,26 @@
     </row>
     <row r="29" ht="24.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I29" s="4"/>
     </row>
